--- a/fhir/activitydefinition-code-to-do-missing-measurement.xlsx
+++ b/fhir/activitydefinition-code-to-do-missing-measurement.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="131">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -198,6 +198,18 @@
     <t>urn:oid:1.2.208.176.2.1</t>
   </si>
   <si>
+    <t>DNK05463</t>
+  </si>
+  <si>
+    <t>DNK05465</t>
+  </si>
+  <si>
+    <t>DNK05467</t>
+  </si>
+  <si>
+    <t>DNK05469</t>
+  </si>
+  <si>
     <t>DNK05472</t>
   </si>
   <si>
@@ -210,6 +222,9 @@
     <t>Blodtryk diastolisk;Arm</t>
   </si>
   <si>
+    <t>NPU02193</t>
+  </si>
+  <si>
     <t>NPU03011</t>
   </si>
   <si>
@@ -282,9 +297,6 @@
     <t>MCS88050</t>
   </si>
   <si>
-    <t>Rejse sætte sig testen;Pt</t>
-  </si>
-  <si>
     <t>MCS88137</t>
   </si>
   <si>
@@ -307,6 +319,9 @@
   </si>
   <si>
     <t>Skridt;Pt</t>
+  </si>
+  <si>
+    <t>MCS88214</t>
   </si>
   <si>
     <t>urn:oid:1.2.208.176.2.4</t>
@@ -865,7 +880,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -906,9 +921,7 @@
       <c r="A3" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>60</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>37</v>
       </c>
@@ -921,11 +934,9 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>62</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>37</v>
       </c>
@@ -938,11 +949,9 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>64</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>37</v>
       </c>
@@ -955,11 +964,9 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>66</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>37</v>
       </c>
@@ -972,10 +979,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>37</v>
@@ -989,10 +996,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>37</v>
@@ -1006,11 +1013,9 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>37</v>
       </c>
@@ -1023,18 +1028,103 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="B10" t="s" s="2">
+      <c r="C12" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="C10" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s" s="2">
+      <c r="B13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E15" t="s" s="2">
         <v>49</v>
       </c>
     </row>
@@ -1045,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1067,7 +1157,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>33</v>
@@ -1084,10 +1174,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>37</v>
@@ -1101,10 +1191,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>37</v>
@@ -1118,10 +1208,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>37</v>
@@ -1135,10 +1225,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>37</v>
@@ -1152,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>37</v>
@@ -1169,11 +1259,9 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>87</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>37</v>
       </c>
@@ -1186,10 +1274,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>37</v>
@@ -1203,10 +1291,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>37</v>
@@ -1220,10 +1308,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>37</v>
@@ -1237,10 +1325,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>37</v>
@@ -1249,6 +1337,21 @@
         <v>48</v>
       </c>
       <c r="E12" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s" s="2">
         <v>49</v>
       </c>
     </row>
@@ -1281,7 +1384,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>33</v>
@@ -1298,10 +1401,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>37</v>
@@ -1342,7 +1445,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>33</v>
@@ -1359,10 +1462,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>37</v>
@@ -1379,7 +1482,7 @@
         <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>37</v>
@@ -1396,7 +1499,7 @@
         <v>46</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>37</v>
@@ -1413,7 +1516,7 @@
         <v>44</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>37</v>
@@ -1427,10 +1530,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>37</v>
@@ -1471,7 +1574,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>33</v>
@@ -1488,10 +1591,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>37</v>
@@ -1505,10 +1608,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>37</v>
@@ -1522,10 +1625,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>37</v>
@@ -1539,10 +1642,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>37</v>
@@ -1556,10 +1659,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>37</v>
@@ -1573,10 +1676,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>37</v>
@@ -1617,7 +1720,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>33</v>
@@ -1634,10 +1737,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>37</v>
@@ -1651,10 +1754,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>37</v>
@@ -1668,10 +1771,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>37</v>

--- a/fhir/activitydefinition-code-to-do-missing-measurement.xlsx
+++ b/fhir/activitydefinition-code-to-do-missing-measurement.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/activitydefinition-code-to-do-missing-measurement.xlsx
+++ b/fhir/activitydefinition-code-to-do-missing-measurement.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/activitydefinition-code-to-do-missing-measurement.xlsx
+++ b/fhir/activitydefinition-code-to-do-missing-measurement.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/activitydefinition-code-to-do-missing-measurement.xlsx
+++ b/fhir/activitydefinition-code-to-do-missing-measurement.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/activitydefinition-code-to-do-missing-measurement.xlsx
+++ b/fhir/activitydefinition-code-to-do-missing-measurement.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/activitydefinition-code-to-do-missing-measurement.xlsx
+++ b/fhir/activitydefinition-code-to-do-missing-measurement.xlsx
@@ -14,12 +14,13 @@
     <sheet name="Mapping Table 4" r:id="rId8" sheetId="6"/>
     <sheet name="Mapping Table 5" r:id="rId9" sheetId="7"/>
     <sheet name="Mapping Table 6" r:id="rId10" sheetId="8"/>
+    <sheet name="Mapping Table 7" r:id="rId11" sheetId="9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="139">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -333,6 +334,9 @@
     <t>Hjemmeblodtryksmåling udført af patienten</t>
   </si>
   <si>
+    <t>ZZ5048</t>
+  </si>
+  <si>
     <t>http://snomed.info/sct</t>
   </si>
   <si>
@@ -412,6 +416,27 @@
   </si>
   <si>
     <t>Klinisk foto</t>
+  </si>
+  <si>
+    <t>http://ehealth.sundhed.dk/cs/mds-codes</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-I</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-IA</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-IB</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-II</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-III</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-IV</t>
   </si>
 </sst>
 </file>
@@ -1362,7 +1387,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1413,6 +1438,21 @@
         <v>48</v>
       </c>
       <c r="E3" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>49</v>
       </c>
     </row>
@@ -1445,7 +1485,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>33</v>
@@ -1462,10 +1502,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>37</v>
@@ -1482,7 +1522,7 @@
         <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>37</v>
@@ -1499,7 +1539,7 @@
         <v>46</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>37</v>
@@ -1516,7 +1556,7 @@
         <v>44</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>37</v>
@@ -1530,10 +1570,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>37</v>
@@ -1574,7 +1614,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>33</v>
@@ -1591,10 +1631,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>37</v>
@@ -1608,10 +1648,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>37</v>
@@ -1625,10 +1665,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>37</v>
@@ -1642,10 +1682,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>37</v>
@@ -1659,10 +1699,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>37</v>
@@ -1676,10 +1716,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>37</v>
@@ -1737,10 +1777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>37</v>
@@ -1754,10 +1794,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>37</v>
@@ -1771,10 +1811,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>37</v>
@@ -1783,6 +1823,140 @@
         <v>48</v>
       </c>
       <c r="E5" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s" s="2">
         <v>49</v>
       </c>
     </row>
